--- a/output/xlsx/UC4Demographics--GT-.xlsx
+++ b/output/xlsx/UC4Demographics--GT-.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>1.0</t>
+    <t>2.0</t>
   </si>
   <si>
     <t>Suite Type:</t>

--- a/output/xlsx/UC4Demographics--GT-.xlsx
+++ b/output/xlsx/UC4Demographics--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="47">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>2.0</t>
+    <t>3.0</t>
   </si>
   <si>
     <t>Suite Type:</t>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 4 test case(s)</t>
+    <t>Size: 6 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -126,6 +126,24 @@
   </si>
   <si>
     <t>TC4</t>
+  </si>
+  <si>
+    <t>Alternative Flow 3: An er may enter or</t>
+  </si>
+  <si>
+    <t>patient: An ER may enter or edit their own demographic information according to the data format in Section 4.6 .</t>
+  </si>
+  <si>
+    <t>TC5</t>
+  </si>
+  <si>
+    <t>Alternative Flow 4: A lab tech may enter</t>
+  </si>
+  <si>
+    <t>patient: A Lab Tech may enter or edit their own demographic information according to the data format in Section 4.6 .</t>
+  </si>
+  <si>
+    <t>TC6</t>
   </si>
   <si>
     <t>Exception Flow 1: Invalid data field format</t>
@@ -226,7 +244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -577,13 +595,13 @@
         <v>1.0</v>
       </c>
       <c r="B34" t="s" s="3">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D34" t="s" s="3">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s" s="3">
         <v>27</v>
@@ -597,7 +615,169 @@
         <v>29</v>
       </c>
       <c r="B35" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s" s="0">
         <v>40</v>
+      </c>
+      <c r="C38" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="E39" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B42" t="s" s="3">
+        <v>42</v>
+      </c>
+      <c r="C42" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E42" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F42" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C46" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E47" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B50" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s" s="3">
+        <v>45</v>
+      </c>
+      <c r="E50" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F50" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/output/xlsx/UC4Demographics--GT-.xlsx
+++ b/output/xlsx/UC4Demographics--GT-.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>3.0</t>
+    <t>4.0</t>
   </si>
   <si>
     <t>Suite Type:</t>

--- a/output/xlsx/UC4Demographics--GT-.xlsx
+++ b/output/xlsx/UC4Demographics--GT-.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>4.0</t>
+    <t>6.0</t>
   </si>
   <si>
     <t>Suite Type:</t>

--- a/output/xlsx/UC4Demographics--GT-.xlsx
+++ b/output/xlsx/UC4Demographics--GT-.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>6.0</t>
+    <t>7.0</t>
   </si>
   <si>
     <t>Suite Type:</t>

--- a/output/xlsx/UC4Demographics--GT-.xlsx
+++ b/output/xlsx/UC4Demographics--GT-.xlsx
@@ -29,7 +29,7 @@
     <t xml:space="preserve">Version: </t>
   </si>
   <si>
-    <t>7.0</t>
+    <t>8.0</t>
   </si>
   <si>
     <t>Suite Type:</t>
